--- a/HW1/Submissions/HW1_grades.xlsx
+++ b/HW1/Submissions/HW1_grades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyeonminlee/Documents/GitHub/ModelingClass2025/HW1/HW1-grading/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW1/Submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170B49F4-C9A7-0B41-937B-69F79C59E664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA94EB-5F32-344B-A941-AE7C9D39C1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27480" yWindow="2040" windowWidth="23560" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>No.</t>
   </si>
@@ -63,9 +63,6 @@
     <t>8</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>Q2</t>
   </si>
   <si>
@@ -133,18 +130,6 @@
     <t>Department</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>4 for each model</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -153,114 +138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>청강생</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강정윤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김기표</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김동준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김진일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박윤수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박창현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>양승민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유시오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정진우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조유솜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지수연</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황희준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P0061836</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P0064052</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-23157</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-22790</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021-17625</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2023-11200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2020-10278</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2020-17092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021-19917</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P0063790</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-27971</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-93373</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2020-11251</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>code는 맞는데 typo가 있거나, 보고를 잘못한 경우, -1.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -290,55 +167,66 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>뇌인지과학과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>언어학과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자유전공학부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>심리학과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reported non-existent parameters in MLE parameter estimates (-1.5 × 6 = -9), reported non-existent parameters in LSE estimates (-6), did not plot the LSE results (-6), and reported incorrect SSE values for LSE (-3.5).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reported non-existent parameters in MLE parameter estimates (-1.5 × 6 = -9).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Incorrectly reported parameter b as parameter a for POW1, EXP1, and HYP1 models in the parameter estimates (-1.5).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Missing one-paragraph summary; although the log-likelihood code is correct, the reported values are incorrect (-35/2 = -17.5); reported log-likelihood instead of SSE for LSE (-0.5 × 6 = -3); incorrect SSE and R² reported for LSE HYP2 model (-1).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>산림과학부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Errors in r2_hyp1 calculation (-5), plotting error in EXP1 model (-4), incorrect reporting of POW3 model (reported as the best model even though it does not exist; likely a typo for EXPOW, -1.5), and failure to report parameter estimates although the code is correct (-5).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Although the parameter estimate code is correct, the estimates were not reported (-5); the LSE graph was not drawn (-6); LSE parameter estimates were not reported (-1); and LSE SSE was not reported (-3.5).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Although the code for LSE is perfect but he didn't report the result and discussion (-3)</t>
+    <t>김준하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020-10641</t>
+  </si>
+  <si>
+    <t>2026-27790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박시윤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서평</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-24964</t>
+  </si>
+  <si>
+    <t>소은솔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0067587</t>
+  </si>
+  <si>
+    <t>2022-14875</t>
+  </si>
+  <si>
+    <t>송승빈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021-16837</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장준호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0067586</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황동욱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-26800</t>
+  </si>
+  <si>
+    <t>황현기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -825,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10" style="3" customWidth="1"/>
@@ -848,22 +736,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
@@ -871,27 +759,20 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="4">
-        <v>100</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <f>F2+G2</f>
-        <v>100</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="69" customHeight="1">
@@ -899,489 +780,276 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.5</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <f t="shared" ref="H3:H14" si="0">F3+G3</f>
-        <v>84.5</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="62" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91</v>
-      </c>
-      <c r="G4" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="H4" s="4">
-        <f t="shared" si="0"/>
-        <v>95.5</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>75</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="4">
-        <v>100</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>117</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="45" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>82</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="4">
-        <v>91</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="51" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="4">
-        <v>98.5</v>
-      </c>
-      <c r="G7" s="4">
-        <v>20</v>
-      </c>
-      <c r="H7" s="4">
-        <f t="shared" si="0"/>
-        <v>118.5</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>80</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="63" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="4">
-        <v>95</v>
-      </c>
-      <c r="G8" s="4">
-        <v>9.5</v>
-      </c>
-      <c r="H8" s="4">
-        <v>104.5</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>85</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" ht="76" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="13">
+        <v>30</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="13">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="15">
+        <v>35</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13">
+        <v>6</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="13">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="4">
-        <v>82.5</v>
-      </c>
-      <c r="G9" s="4">
-        <v>16</v>
-      </c>
-      <c r="H9" s="4">
-        <f t="shared" si="0"/>
-        <v>98.5</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="I20" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="15">
+        <v>7</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="4">
-        <v>100</v>
-      </c>
-      <c r="G10" s="4">
-        <v>20</v>
-      </c>
-      <c r="H10" s="4">
-        <f t="shared" si="0"/>
-        <v>120</v>
-      </c>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="4">
-        <v>100</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="4">
-        <v>100</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="4">
-        <v>100</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" s="3" customFormat="1" ht="31" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="4">
-        <v>100</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="19"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="11"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="13">
-        <v>30</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="13">
-        <v>35</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="15">
-        <v>35</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="3" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="13">
-        <v>6</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="13">
-        <v>7</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="A23" s="17" t="s">
         <v>29</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="15">
-        <v>7</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="17" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="1">
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HW1/Submissions/HW1_grades.xlsx
+++ b/HW1/Submissions/HW1_grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW1/Submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA94EB-5F32-344B-A941-AE7C9D39C1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364F70DD-499D-EF46-AFDB-6339412CC919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8380" yWindow="660" windowWidth="19500" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -227,6 +227,10 @@
   </si>
   <si>
     <t>황현기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 피규어가 다름. 코드에 오류 존재</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -358,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -408,6 +412,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -770,10 +777,14 @@
       <c r="E2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="20">
+        <v>98.5</v>
+      </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="69" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -808,7 +819,9 @@
       <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4">
+        <v>100</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -827,7 +840,9 @@
       <c r="E5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -884,7 +899,9 @@
       <c r="E8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="4">
+        <v>100</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -903,7 +920,9 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4">
+        <v>100</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>

--- a/HW1/Submissions/HW1_grades.xlsx
+++ b/HW1/Submissions/HW1_grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW1/Submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364F70DD-499D-EF46-AFDB-6339412CC919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B304B72C-D24C-A048-8068-D0E0F2D887D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8380" yWindow="660" windowWidth="19500" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
   <si>
     <t>No.</t>
   </si>
@@ -230,7 +230,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 피규어가 다름. 코드에 오류 존재</t>
+    <t>1. 피규어가 다름 (-4)
+2. 코드에 오류 존재 (-1.5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. MLE 피규어 다름. 코드에 오류 있음 (-4)
+2. MLE 파라미터 추정 값 HYP2가 다름 (-5)
+3. MLE log likelihood HYP2가 다름 (-5)
+4. MLE 코드 오류 존재 (-1.5)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -407,14 +415,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -761,7 +769,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
+    <row r="2" spans="1:9" s="3" customFormat="1" ht="50" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,8 +785,8 @@
       <c r="E2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="20">
-        <v>98.5</v>
+      <c r="F2" s="18">
+        <v>94.5</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -800,9 +808,15 @@
       <c r="E3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="F3" s="4">
+        <v>100</v>
+      </c>
+      <c r="G3" s="4">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4">
+        <v>120</v>
+      </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="62" customHeight="1">
@@ -847,7 +861,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9" s="3" customFormat="1" ht="45" customHeight="1">
+    <row r="6" spans="1:9" s="3" customFormat="1" ht="93" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -861,10 +875,14 @@
       <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <v>84.5</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="6"/>
+      <c r="I6" s="6" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="51" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -880,7 +898,9 @@
       <c r="E7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <v>100</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -939,10 +959,10 @@
       <c r="I10" s="8"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="20"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="10" t="s">

--- a/HW1/Submissions/HW1_grades.xlsx
+++ b/HW1/Submissions/HW1_grades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Desktop/GitHub/2026_Computational-Modeling/HW1/Submissions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kangjungyoon/Documents/GitHub/2026_Computational-Modeling/HW1/Submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B304B72C-D24C-A048-8068-D0E0F2D887D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4C56C1-D470-5940-9F78-BB498E6E9AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="16440" windowWidth="28360" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
   <si>
     <t>No.</t>
   </si>
@@ -230,15 +230,33 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 피규어가 다름 (-4)
-2. 코드에 오류 존재 (-1.5)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. MLE 피규어 다름. 코드에 오류 있음 (-4)
-2. MLE 파라미터 추정 값 HYP2가 다름 (-5)
-3. MLE log likelihood HYP2가 다름 (-5)
-4. MLE 코드 오류 존재 (-1.5)</t>
+    <t>5 for each model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. LSE 플랏 없음 (-6)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. EXP1 mle 피규어 다름. 코드 오류 (-2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. MLE 피규어 다름. 코드에 오류 있음 (-2)
+2. MLE 파라미터 추정 값 HYP2가 다름 (-2.5)
+3. MLE log likelihood HYP2가 다름 (-2.5)
+4. 지각 제출 -10% (-9.3)
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 한글제출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 피규어만 있음. Pdf 미제출
+2. MLE 미제출 (-35)
+3. r square 미제출 (-35)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -786,12 +804,14 @@
         <v>41</v>
       </c>
       <c r="F2" s="18">
-        <v>94.5</v>
+        <v>98</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4">
+        <v>98</v>
+      </c>
       <c r="I2" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="69" customHeight="1">
@@ -834,11 +854,15 @@
         <v>33</v>
       </c>
       <c r="F4" s="4">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="H4" s="4">
+        <v>30</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -858,7 +882,9 @@
         <v>100</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4">
+        <v>100</v>
+      </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="93" customHeight="1">
@@ -876,12 +902,13 @@
         <v>33</v>
       </c>
       <c r="F6" s="4">
-        <v>84.5</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="H6" s="4">
+        <v>83.7</v>
+      </c>
       <c r="I6" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="51" customHeight="1">
@@ -902,8 +929,12 @@
         <v>100</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="H7" s="4">
+        <v>100</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="63" customHeight="1">
       <c r="A8" s="1" t="s">
@@ -922,9 +953,15 @@
       <c r="F8" s="4">
         <v>100</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="G8" s="4">
+        <v>14</v>
+      </c>
+      <c r="H8" s="4">
+        <v>114</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" ht="76" customHeight="1">
       <c r="A9" s="1" t="s">
@@ -944,7 +981,9 @@
         <v>100</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4">
+        <v>100</v>
+      </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" ht="25" customHeight="1">
@@ -1009,7 +1048,7 @@
         <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>36</v>
